--- a/BVSimulationFiles/96.xlsx
+++ b/BVSimulationFiles/96.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000198581560283688</v>
+        <v>0.000397163120567376</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002035291494446851</v>
+        <v>0.0004070582988893702</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002079284904985453</v>
+        <v>0.0004158569809970906</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002118105617442589</v>
+        <v>0.0004236211234885178</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002152048878897823</v>
+        <v>0.0004304097757795646</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002181396024559869</v>
+        <v>0.0004362792049119738</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002206415076381626</v>
+        <v>0.0004412830152763252</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002227361317251402</v>
+        <v>0.0004454722634502804</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002244477841722618</v>
+        <v>0.0004488955683445236</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000225799608420723</v>
+        <v>0.000451599216841446</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002268136325522574</v>
+        <v>0.0004536272651045148</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0002275108178647058</v>
+        <v>0.0004550216357294116</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0002279111054507199</v>
+        <v>0.0004558222109014398</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002280334608586762</v>
+        <v>0.0004560669217173524</v>
       </c>
       <c r="P2" t="n">
-        <v>0.000227895916911831</v>
+        <v>0.000455791833823662</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002275156147588046</v>
+        <v>0.0004550312295176092</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0002269088432256658</v>
+        <v>0.0004538176864513316</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002260910765371653</v>
+        <v>0.0004521821530743306</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000225077010472057</v>
+        <v>0.000450154020944114</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002238805970149253</v>
+        <v>0.0004477611940298506</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000198581560283688</v>
+        <v>0.000397163120567376</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002035291494446851</v>
+        <v>0.0004070582988893702</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002079284904985453</v>
+        <v>0.0004158569809970906</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002118105617442589</v>
+        <v>0.0004236211234885178</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002152048878897823</v>
+        <v>0.0004304097757795646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002181396024559869</v>
+        <v>0.0004362792049119738</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0002206415076381626</v>
+        <v>0.0004412830152763252</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002227361317251402</v>
+        <v>0.0004454722634502804</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002244477841722618</v>
+        <v>0.0004488955683445236</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000225799608420723</v>
+        <v>0.000451599216841446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002268136325522574</v>
+        <v>0.0004536272651045148</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002275108178647058</v>
+        <v>0.0004550216357294116</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0002279111054507199</v>
+        <v>0.0004558222109014398</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0002280334608586762</v>
+        <v>0.0004560669217173524</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000227895916911831</v>
+        <v>0.000455791833823662</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002275156147588046</v>
+        <v>0.0004550312295176092</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002269088432256658</v>
+        <v>0.0004538176864513316</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002260910765371653</v>
+        <v>0.0004521821530743306</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000225077010472057</v>
+        <v>0.000450154020944114</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0002238805970149253</v>
+        <v>0.0004477611940298506</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/96.xlsx
+++ b/BVSimulationFiles/96.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000397163120567376</v>
+        <v>0.00397163120567376</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004070582988893702</v>
+        <v>0.004070582988893702</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004158569809970906</v>
+        <v>0.004158569809970906</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004236211234885178</v>
+        <v>0.004236211234885178</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004304097757795646</v>
+        <v>0.004304097757795645</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004362792049119738</v>
+        <v>0.004362792049119739</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0004412830152763252</v>
+        <v>0.004412830152763252</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004454722634502804</v>
+        <v>0.004454722634502804</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004488955683445236</v>
+        <v>0.004488955683445236</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000451599216841446</v>
+        <v>0.00451599216841446</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004536272651045148</v>
+        <v>0.004536272651045148</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004550216357294116</v>
+        <v>0.004550216357294116</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004558222109014398</v>
+        <v>0.004558222109014398</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0004560669217173524</v>
+        <v>0.004560669217173524</v>
       </c>
       <c r="P2" t="n">
-        <v>0.000455791833823662</v>
+        <v>0.00455791833823662</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0004550312295176092</v>
+        <v>0.004550312295176092</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0004538176864513316</v>
+        <v>0.004538176864513317</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004521821530743306</v>
+        <v>0.004521821530743306</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000450154020944114</v>
+        <v>0.00450154020944114</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0004477611940298506</v>
+        <v>0.004477611940298506</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000397163120567376</v>
+        <v>0.00397163120567376</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004070582988893702</v>
+        <v>0.004070582988893702</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004158569809970906</v>
+        <v>0.004158569809970906</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004236211234885178</v>
+        <v>0.004236211234885178</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004304097757795646</v>
+        <v>0.004304097757795645</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004362792049119738</v>
+        <v>0.004362792049119739</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004412830152763252</v>
+        <v>0.004412830152763252</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004454722634502804</v>
+        <v>0.004454722634502804</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004488955683445236</v>
+        <v>0.004488955683445236</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000451599216841446</v>
+        <v>0.00451599216841446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004536272651045148</v>
+        <v>0.004536272651045148</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004550216357294116</v>
+        <v>0.004550216357294116</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004558222109014398</v>
+        <v>0.004558222109014398</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0004560669217173524</v>
+        <v>0.004560669217173524</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000455791833823662</v>
+        <v>0.00455791833823662</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004550312295176092</v>
+        <v>0.004550312295176092</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004538176864513316</v>
+        <v>0.004538176864513317</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004521821530743306</v>
+        <v>0.004521821530743306</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000450154020944114</v>
+        <v>0.00450154020944114</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004477611940298506</v>
+        <v>0.004477611940298506</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/96.xlsx
+++ b/BVSimulationFiles/96.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,61 +421,49 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.02513947368421053</v>
+        <v>0.01647068965517241</v>
       </c>
       <c r="D1" t="n">
-        <v>0.05027894736842105</v>
+        <v>0.03294137931034483</v>
       </c>
       <c r="E1" t="n">
-        <v>0.07541842105263158</v>
+        <v>0.04941206896551725</v>
       </c>
       <c r="F1" t="n">
-        <v>0.1005578947368421</v>
+        <v>0.06588275862068965</v>
       </c>
       <c r="G1" t="n">
-        <v>0.1256973684210526</v>
+        <v>0.08235344827586207</v>
       </c>
       <c r="H1" t="n">
-        <v>0.1508368421052632</v>
+        <v>0.09882413793103449</v>
       </c>
       <c r="I1" t="n">
-        <v>0.1759763157894737</v>
+        <v>0.1152948275862069</v>
       </c>
       <c r="J1" t="n">
-        <v>0.2011157894736842</v>
+        <v>0.1317655172413793</v>
       </c>
       <c r="K1" t="n">
-        <v>0.2262552631578948</v>
+        <v>0.1482362068965517</v>
       </c>
       <c r="L1" t="n">
-        <v>0.2513947368421053</v>
+        <v>0.1647068965517241</v>
       </c>
       <c r="M1" t="n">
-        <v>0.2765342105263158</v>
+        <v>0.1811775862068966</v>
       </c>
       <c r="N1" t="n">
-        <v>0.3016736842105263</v>
+        <v>0.197648275862069</v>
       </c>
       <c r="O1" t="n">
-        <v>0.3268131578947369</v>
+        <v>0.2141189655172414</v>
       </c>
       <c r="P1" t="n">
-        <v>0.3519526315789474</v>
+        <v>0.2305896551724138</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.377092105263158</v>
-      </c>
-      <c r="R1" t="n">
-        <v>0.4022315789473684</v>
-      </c>
-      <c r="S1" t="n">
-        <v>0.4273710526315789</v>
-      </c>
-      <c r="T1" t="n">
-        <v>0.4525105263157895</v>
-      </c>
-      <c r="U1" t="n">
-        <v>0.47765</v>
+        <v>0.2470603448275862</v>
       </c>
     </row>
     <row r="2">
@@ -483,64 +471,52 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00397163120567376</v>
+        <v>0.02411415422014783</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004070582988893702</v>
+        <v>0.0248270783193614</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004158569809970906</v>
+        <v>0.02543296401954236</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004236211234885178</v>
+        <v>0.02593974799618091</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004304097757795645</v>
+        <v>0.02635488012902083</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004362792049119739</v>
+        <v>0.02668535078532269</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004412830152763252</v>
+        <v>0.02693771665277545</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004454722634502804</v>
+        <v>0.02711812519651702</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004488955683445236</v>
+        <v>0.02723233781099476</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00451599216841446</v>
+        <v>0.02728575173385125</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004536272651045148</v>
+        <v>0.02728342078564816</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004550216357294116</v>
+        <v>0.02723007499603583</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004558222109014398</v>
+        <v>0.02713013917392843</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004560669217173524</v>
+        <v>0.02698775047634733</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00455791833823662</v>
+        <v>0.02680677502784062</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004550312295176092</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.004538176864513317</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.004521821530743306</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.00450154020944114</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.004477611940298506</v>
+        <v>0.02659082363976865</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +524,52 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00397163120567376</v>
+        <v>0.02411415422014783</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004070582988893702</v>
+        <v>0.0248270783193614</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004158569809970906</v>
+        <v>0.02543296401954236</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004236211234885178</v>
+        <v>0.02593974799618091</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004304097757795645</v>
+        <v>0.02635488012902083</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004362792049119739</v>
+        <v>0.02668535078532269</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004412830152763252</v>
+        <v>0.02693771665277545</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004454722634502804</v>
+        <v>0.02711812519651702</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004488955683445236</v>
+        <v>0.02723233781099476</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00451599216841446</v>
+        <v>0.02728575173385125</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004536272651045148</v>
+        <v>0.02728342078564816</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004550216357294116</v>
+        <v>0.02723007499603583</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004558222109014398</v>
+        <v>0.02713013917392843</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004560669217173524</v>
+        <v>0.02698775047634733</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00455791833823662</v>
+        <v>0.02680677502784062</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004550312295176092</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.004538176864513317</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.004521821530743306</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.00450154020944114</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.004477611940298506</v>
+        <v>0.02659082363976865</v>
       </c>
     </row>
   </sheetData>
